--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23272,7 +23272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23492,200 +23492,204 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Burnett's Vodka 1.75L</t>
+          <t>Bulleit Bourbon 750ml</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>096749200313</t>
+          <t>087000005525</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="I4" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>10.13</v>
+        <v>19.26</v>
       </c>
       <c r="N4" t="n">
-        <v>182</v>
+        <v>2773</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Jan, Apr, Jul, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Captain Morgan Spiced Rum 1.75L</t>
+          <t>Burnett's Vodka 1.75L</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>082000759102</t>
+          <t>096749200313</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>718</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>201</v>
+        <v>32.5</v>
       </c>
       <c r="I5" t="n">
-        <v>237</v>
+        <v>49</v>
       </c>
       <c r="J5" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="K5" t="n">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>19.5</v>
+        <v>10.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3042</v>
+        <v>182</v>
       </c>
       <c r="O5" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Jan, Apr, Jul, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Carolans Irish Cream 750ml</t>
+          <t>Captain Morgan Spiced Rum 1.75L</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>721059517508</t>
+          <t>082000759102</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>718</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>-4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>201</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>237</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="M6" t="n">
-        <v>10.68</v>
+        <v>19.5</v>
       </c>
       <c r="N6" t="n">
-        <v>128</v>
+        <v>3042</v>
       </c>
       <c r="O6" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Mar, Jun, Aug, Nov, Dec)</t>
+          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cazadores Reposado 1.75L</t>
+          <t>Carolans Irish Cream 750ml</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>080480170004</t>
+          <t>721059517508</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23694,59 +23698,59 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>29.74</v>
+        <v>10.68</v>
       </c>
       <c r="N7" t="n">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="O7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Mar, Jun, Aug, Nov, Dec)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christian Brothers Brandy 1.75L</t>
+          <t>Cazadores Reposado 1.75L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>086036815474</t>
+          <t>080480170004</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23755,59 +23759,59 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>29.5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>14.78</v>
+        <v>29.74</v>
       </c>
       <c r="N8" t="n">
-        <v>887</v>
+        <v>178</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Mar, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deep Eddy Lemon Liter</t>
+          <t>Christian Brothers Brandy 1.75L</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>856065002424</t>
+          <t>086036815474</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23816,37 +23820,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5</v>
+        <v>29.5</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="n">
         <v>10</v>
       </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
       <c r="M9" t="n">
-        <v>14.46</v>
+        <v>14.78</v>
       </c>
       <c r="N9" t="n">
-        <v>173</v>
+        <v>887</v>
       </c>
       <c r="O9" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23858,17 +23862,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evan Williams 100 Proof 1.75L</t>
+          <t>Deep Eddy Lemon Liter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>096749021178</t>
+          <t>856065002424</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23877,54 +23881,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-2</v>
+        <v>43</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="I10" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
         <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>21.87</v>
+        <v>14.46</v>
       </c>
       <c r="N10" t="n">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Jan, Apr, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Mar, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Glenlivet Caribbean Reserve 750ml</t>
+          <t>Evan Williams 100 Proof 1.75L</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>080432115763</t>
+          <t>096749021178</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -23938,95 +23942,95 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="G11" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>30.26</v>
+        <v>21.87</v>
       </c>
       <c r="N11" t="n">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="O11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
+          <t>Wait for buy-month (Jan, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Glenlivet Caribbean Reserve 750ml</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>085000429273</t>
+          <t>080432115763</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H12" t="n">
-        <v>33.2</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>8.75</v>
+        <v>30.26</v>
       </c>
       <c r="N12" t="n">
-        <v>473</v>
+        <v>182</v>
       </c>
       <c r="O12" t="n">
         <v>37</v>
@@ -24034,19 +24038,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Wait for buy-month (May, Aug)</t>
+          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>085000426272</t>
+          <t>085000429273</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24060,37 +24064,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
         <v>-7</v>
       </c>
       <c r="H13" t="n">
-        <v>31.5</v>
+        <v>33.2</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M13" t="n">
-        <v>8.59</v>
+        <v>8.75</v>
       </c>
       <c r="N13" t="n">
-        <v>309</v>
+        <v>473</v>
       </c>
       <c r="O13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24102,12 +24106,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>085000430958</t>
+          <t>085000426272</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24121,37 +24125,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>31.5</v>
       </c>
       <c r="I14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>8.470000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="N14" t="n">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="O14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24163,12 +24167,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>085000431375</t>
+          <t>085000430958</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24182,37 +24186,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-25</v>
+        <v>-3</v>
       </c>
       <c r="H15" t="n">
-        <v>53.8</v>
+        <v>22</v>
       </c>
       <c r="I15" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>8.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>312</v>
+        <v>203</v>
       </c>
       <c r="O15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24224,12 +24228,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>085000429266</t>
+          <t>085000431375</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24243,34 +24247,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="H16" t="n">
-        <v>60.2</v>
+        <v>53.8</v>
       </c>
       <c r="I16" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="J16" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>8.76</v>
+        <v>8.67</v>
       </c>
       <c r="N16" t="n">
-        <v>525</v>
+        <v>312</v>
       </c>
       <c r="O16" t="n">
         <v>37</v>
@@ -24285,73 +24289,73 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ketel One Vodka 1.75L</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>085156803682</t>
+          <t>085000429266</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Pre-Mix</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>339</v>
+        <v>101</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="H17" t="n">
-        <v>55.8</v>
+        <v>60.2</v>
       </c>
       <c r="I17" t="n">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="J17" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>25.79</v>
+        <v>8.76</v>
       </c>
       <c r="N17" t="n">
-        <v>1083</v>
+        <v>525</v>
       </c>
       <c r="O17" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (May, Aug)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ketel One Vodka 750ml</t>
+          <t>Ketel One Vodka 1.75L</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>085156515417</t>
+          <t>085156803682</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24361,41 +24365,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>339</v>
       </c>
       <c r="F18" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="H18" t="n">
-        <v>18.8</v>
+        <v>55.8</v>
       </c>
       <c r="I18" t="n">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="J18" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>14.67</v>
+        <v>25.79</v>
       </c>
       <c r="N18" t="n">
-        <v>176</v>
+        <v>1083</v>
       </c>
       <c r="O18" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24407,41 +24411,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Malibu Rum Strawberry Liter</t>
+          <t>Ketel One Vodka 750ml</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>089540540115</t>
+          <t>085156515417</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E19" t="n">
+        <v>93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G19" t="n">
         <v>9</v>
       </c>
-      <c r="F19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>104</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>18.8</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
@@ -24450,35 +24454,35 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>15.12</v>
+        <v>14.67</v>
       </c>
       <c r="N19" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O19" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
+          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sauza Hornitos Plata 750ml</t>
+          <t>Malibu Rum Strawberry Liter</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>080686835325</t>
+          <t>089540540115</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -24487,54 +24491,54 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="H20" t="n">
-        <v>30.2</v>
+        <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>181</v>
+      </c>
+      <c r="O20" t="n">
         <v>24</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="N20" t="n">
-        <v>351</v>
-      </c>
-      <c r="O20" t="n">
-        <v>39</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, May, Aug, Oct, Nov)</t>
+          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sauza Hornitos Plata Tequila 1.75L</t>
+          <t>Sauza Hornitos Plata 750ml</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>080686835349</t>
+          <t>080686835325</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24548,37 +24552,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>20.8</v>
+        <v>30.2</v>
       </c>
       <c r="I21" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>28.94</v>
+        <v>14.63</v>
       </c>
       <c r="N21" t="n">
-        <v>521</v>
+        <v>351</v>
       </c>
       <c r="O21" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24590,77 +24594,73 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Smirnoff Vodka Liter</t>
+          <t>Sauza Hornitos Plata Tequila 1.75L</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08200501</t>
+          <t>080686835349</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>33.8</v>
+        <v>20.8</v>
       </c>
       <c r="I22" t="n">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="J22" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>10.35</v>
+        <v>28.94</v>
       </c>
       <c r="N22" t="n">
-        <v>869</v>
+        <v>521</v>
       </c>
       <c r="O22" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Feb, Apr, May, Aug, Oct, Nov)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Svedka Blue Raspberry Vodka Liter</t>
+          <t>Smirnoff Vodka Liter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>617768201107</t>
+          <t>08200501</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -24670,58 +24670,62 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>33.8</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>9.75</v>
+        <v>10.35</v>
       </c>
       <c r="N23" t="n">
-        <v>117</v>
+        <v>869</v>
       </c>
       <c r="O23" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
+          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Svedka Strawberry Vodka 1.75L</t>
+          <t>Svedka Blue Raspberry Vodka Liter</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>088004072063</t>
+          <t>617768201107</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -24735,37 +24739,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>14.62</v>
+        <v>9.75</v>
       </c>
       <c r="N24" t="n">
-        <v>351</v>
+        <v>117</v>
       </c>
       <c r="O24" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24777,12 +24781,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Svedka Vanilla Vodka 1.75L</t>
+          <t>Svedka Strawberry Vodka 1.75L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>088004071929</t>
+          <t>088004072063</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -24796,34 +24800,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
         <v>14.62</v>
       </c>
       <c r="N25" t="n">
-        <v>88</v>
+        <v>351</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
@@ -24838,12 +24842,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Svedka Vodka Traveler</t>
+          <t>Svedka Vanilla Vodka 1.75L</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>617768121757</t>
+          <t>088004071929</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -24857,101 +24861,162 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-14</v>
+        <v>73</v>
       </c>
       <c r="H26" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K26" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>7.29</v>
+        <v>14.62</v>
       </c>
       <c r="N26" t="n">
-        <v>962</v>
+        <v>88</v>
       </c>
       <c r="O26" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, May, Aug, Nov, Dec)</t>
+          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Windsor Canadian 1.75L</t>
+          <t>Svedka Vodka Traveler</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>080686500124</t>
+          <t>617768121757</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>340</v>
+        <v>153</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>-14</v>
       </c>
       <c r="H27" t="n">
-        <v>127.2</v>
+        <v>24</v>
       </c>
       <c r="I27" t="n">
-        <v>221</v>
+        <v>148</v>
       </c>
       <c r="J27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="L27" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>25.56</v>
+        <v>7.29</v>
       </c>
       <c r="N27" t="n">
-        <v>5213</v>
+        <v>962</v>
       </c>
       <c r="O27" t="n">
-        <v>-50</v>
+        <v>44</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (Feb, May, Aug, Nov, Dec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Windsor Canadian 1.75L</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>080686500124</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Whisky/Whiskey</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>340</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>221</v>
+      </c>
+      <c r="J28" t="n">
+        <v>17</v>
+      </c>
+      <c r="K28" t="n">
+        <v>204</v>
+      </c>
+      <c r="L28" t="n">
+        <v>34</v>
+      </c>
+      <c r="M28" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5213</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-50</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>Wait for buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec)</t>
         </is>

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1684,21 +1684,25 @@
         <v>45</v>
       </c>
       <c r="K21" t="n">
-        <v>240</v>
+        <v>720</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
         <v>0.67</v>
       </c>
       <c r="N21" t="n">
-        <v>161</v>
+        <v>482</v>
       </c>
       <c r="O21" t="n">
         <v>55</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
     </row>

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18598,7 +18598,11 @@
       <c r="O15" t="n">
         <v>29</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18598,11 +18598,7 @@
       <c r="O15" t="n">
         <v>29</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
